--- a/projects_data/AutoPatternmaker/Armstrong.xlsx
+++ b/projects_data/AutoPatternmaker/Armstrong.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sxia2\Documents\GitHub\sxia2.github.io\projects_data\AutoPatternmaker\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibeixia\Documents\GitHub\sibeixia.github.io\projects_data\AutoPatternmaker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64AE1E7-9E02-4F4F-9D61-B3215C91ED6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23AAB69-7A80-4EA6-A363-F8DC81BDE068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17136" yWindow="8520" windowWidth="6696" windowHeight="5232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18885" yWindow="3210" windowWidth="14400" windowHeight="8175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Armstrong" sheetId="1" r:id="rId1"/>
@@ -744,9 +744,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -784,7 +784,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -890,7 +890,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1032,7 +1032,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1041,9 +1041,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="24.26953125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>51</v>
       </c>
@@ -1060,7 +1063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1077,7 +1080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1094,7 +1097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1111,7 +1114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1128,7 +1131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1145,7 +1148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1162,7 +1165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1179,7 +1182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1196,7 +1199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1213,7 +1216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>7</v>
       </c>
@@ -1230,7 +1233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>8</v>
       </c>
@@ -1247,7 +1250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>9</v>
       </c>
@@ -1264,7 +1267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>9</v>
       </c>
@@ -1281,7 +1284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>10</v>
       </c>
@@ -1298,7 +1301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>11</v>
       </c>
@@ -1315,7 +1318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>12</v>
       </c>
@@ -1332,7 +1335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>13</v>
       </c>
@@ -1349,7 +1352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>14</v>
       </c>
@@ -1366,7 +1369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>14</v>
       </c>
@@ -1383,7 +1386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>15</v>
       </c>
@@ -1400,7 +1403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>16</v>
       </c>
@@ -1417,7 +1420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>17</v>
       </c>
@@ -1434,7 +1437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>18</v>
       </c>
@@ -1451,7 +1454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>19</v>
       </c>
@@ -1468,7 +1471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>19</v>
       </c>
@@ -1485,7 +1488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>20</v>
       </c>
@@ -1502,7 +1505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>20</v>
       </c>
@@ -1519,7 +1522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>22</v>
       </c>
@@ -1536,7 +1539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>22</v>
       </c>
@@ -1553,7 +1556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>23</v>
       </c>
@@ -1570,7 +1573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>23</v>
       </c>
@@ -1587,7 +1590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>24</v>
       </c>
@@ -1604,7 +1607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>25</v>
       </c>
@@ -1621,7 +1624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>25</v>
       </c>
@@ -1638,7 +1641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>26</v>
       </c>
@@ -1655,7 +1658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>27</v>
       </c>
@@ -1672,7 +1675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>27</v>
       </c>
@@ -1689,7 +1692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>27</v>
       </c>
@@ -1706,7 +1709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>28</v>
       </c>
@@ -1723,7 +1726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>28</v>
       </c>
@@ -1740,7 +1743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>29</v>
       </c>
@@ -1757,7 +1760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>29</v>
       </c>
@@ -1774,7 +1777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>30</v>
       </c>
@@ -1791,7 +1794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>31</v>
       </c>
@@ -1808,7 +1811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>32</v>
       </c>
@@ -1825,7 +1828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>32</v>
       </c>
@@ -1842,7 +1845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -1859,7 +1862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -1876,7 +1879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>54</v>
       </c>
